--- a/materials/Excel_in_class_exercises.xlsx
+++ b/materials/Excel_in_class_exercises.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Introduction to Programming\Exercises_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BF4435-BC04-4D75-9943-DAC06CFFC008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8204ED34-E384-4DF0-B4A7-2F78FD7DA1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25035" windowHeight="14310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Future_Value" sheetId="9" r:id="rId1"/>
@@ -22,10 +22,11 @@
     <sheet name="Installment" sheetId="13" r:id="rId7"/>
     <sheet name="Annuity" sheetId="6" r:id="rId8"/>
     <sheet name="Exam" sheetId="20" r:id="rId9"/>
-    <sheet name="Bar_Sales" sheetId="24" r:id="rId10"/>
-    <sheet name="Gift" sheetId="29" r:id="rId11"/>
-    <sheet name="Grading" sheetId="25" r:id="rId12"/>
-    <sheet name="Clients" sheetId="33" r:id="rId13"/>
+    <sheet name="Department" sheetId="34" r:id="rId10"/>
+    <sheet name="Bar_Sales" sheetId="24" r:id="rId11"/>
+    <sheet name="Gift" sheetId="29" r:id="rId12"/>
+    <sheet name="Grading" sheetId="25" r:id="rId13"/>
+    <sheet name="Clients" sheetId="33" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="solver_corr" hidden="1">1</definedName>
@@ -45,24 +46,11 @@
     <definedName name="solver_ucut" hidden="1">1E+30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="157">
   <si>
     <t>DAX</t>
   </si>
@@ -473,6 +461,66 @@
   </si>
   <si>
     <t>City:</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Hooloway</t>
+  </si>
+  <si>
+    <t>Clark</t>
+  </si>
+  <si>
+    <t>Taylor</t>
+  </si>
+  <si>
+    <t>Foster</t>
+  </si>
+  <si>
+    <t>Watson</t>
+  </si>
+  <si>
+    <t>Dawkins</t>
+  </si>
+  <si>
+    <t>Parker</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>Credit</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Number of people in the Credit Department</t>
+  </si>
+  <si>
+    <t>Sum of salaries in the Credit Department</t>
+  </si>
+  <si>
+    <t>Average salary in the Credit Department</t>
+  </si>
+  <si>
+    <t>Number of people with salary&lt;200000</t>
+  </si>
+  <si>
+    <t>Sum of these salaries</t>
+  </si>
+  <si>
+    <t>Average of these salaries</t>
   </si>
 </sst>
 </file>
@@ -480,8 +528,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -712,10 +760,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -788,17 +836,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
@@ -841,6 +889,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Currency 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1290,6 +1339,139 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEFCE2C8-4468-4C3C-8B6F-65072CE7A456}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="37.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="63" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2">
+        <v>300000</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3">
+        <v>270000</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4">
+        <v>180000</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5">
+        <v>235000</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6">
+        <v>150000</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7">
+        <v>420000</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8">
+        <v>305000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9">
+        <v>195000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B1:H28"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1536,7 +1718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B2:H22"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -1937,7 +2119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -2290,7 +2472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
